--- a/tables/Solid_waste_pt.xlsx
+++ b/tables/Solid_waste_pt.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\pucc\solid_waste_Data_Analysis_Study\tables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1848e9536f9f8e2e/Documentos/GitHub/Solid_Waste_Data_Analysis_Study/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEE2A7F0-8F4E-4449-8D35-44DBE395A750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{EEE2A7F0-8F4E-4449-8D35-44DBE395A750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DEC80032-7EC8-4F6F-9561-783C75C54D17}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados" sheetId="1" r:id="rId1"/>
@@ -506,23 +506,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:K301"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.44140625" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="14.77734375" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="23.42578125" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="5" width="20" hidden="1" customWidth="1"/>
+    <col min="4" max="5" width="20" customWidth="1"/>
     <col min="6" max="6" width="25" customWidth="1"/>
-    <col min="7" max="7" width="22" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="26" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="33" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="29" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="26" customWidth="1"/>
+    <col min="9" max="9" width="33" customWidth="1"/>
+    <col min="10" max="10" width="29" customWidth="1"/>
     <col min="11" max="11" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -557,7 +556,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>15</v>
       </c>
@@ -592,7 +591,7 @@
         <v>19.2</v>
       </c>
     </row>
-    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>17</v>
       </c>
@@ -627,7 +626,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>24</v>
       </c>
@@ -662,7 +661,7 @@
         <v>17.399999999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>24</v>
       </c>
@@ -697,7 +696,7 @@
         <v>11.9</v>
       </c>
     </row>
-    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
@@ -732,7 +731,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>15</v>
       </c>
@@ -767,7 +766,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
@@ -802,7 +801,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>20</v>
       </c>
@@ -837,7 +836,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
@@ -872,7 +871,7 @@
         <v>9.3000000000000007</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
@@ -907,7 +906,7 @@
         <v>9.6999999999999993</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>24</v>
       </c>
@@ -942,7 +941,7 @@
         <v>9.6999999999999993</v>
       </c>
     </row>
-    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
@@ -977,7 +976,7 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>17</v>
       </c>
@@ -1012,7 +1011,7 @@
         <v>9.3000000000000007</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>24</v>
       </c>
@@ -1047,7 +1046,7 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>17</v>
       </c>
@@ -1082,7 +1081,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>15</v>
       </c>
@@ -1117,7 +1116,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>24</v>
       </c>
@@ -1152,7 +1151,7 @@
         <v>8.8000000000000007</v>
       </c>
     </row>
-    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>24</v>
       </c>
@@ -1187,7 +1186,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>20</v>
       </c>
@@ -1222,7 +1221,7 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>11</v>
       </c>
@@ -1257,7 +1256,7 @@
         <v>9.3000000000000007</v>
       </c>
     </row>
-    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>20</v>
       </c>
@@ -1292,7 +1291,7 @@
         <v>9.3000000000000007</v>
       </c>
     </row>
-    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>24</v>
       </c>
@@ -1327,7 +1326,7 @@
         <v>9.1</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>15</v>
       </c>
@@ -1362,7 +1361,7 @@
         <v>9.1</v>
       </c>
     </row>
-    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>24</v>
       </c>
@@ -1397,7 +1396,7 @@
         <v>8.8000000000000007</v>
       </c>
     </row>
-    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>17</v>
       </c>
@@ -1432,7 +1431,7 @@
         <v>9.4</v>
       </c>
     </row>
-    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>17</v>
       </c>
@@ -1467,7 +1466,7 @@
         <v>19.2</v>
       </c>
     </row>
-    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>11</v>
       </c>
@@ -1502,7 +1501,7 @@
         <v>19.2</v>
       </c>
     </row>
-    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>11</v>
       </c>
@@ -1537,7 +1536,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>17</v>
       </c>
@@ -1572,7 +1571,7 @@
         <v>17.7</v>
       </c>
     </row>
-    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>15</v>
       </c>
@@ -1607,7 +1606,7 @@
         <v>8.8000000000000007</v>
       </c>
     </row>
-    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>15</v>
       </c>
@@ -1642,7 +1641,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>20</v>
       </c>
@@ -1677,7 +1676,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>15</v>
       </c>
@@ -1712,7 +1711,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>11</v>
       </c>
@@ -1747,7 +1746,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>17</v>
       </c>
@@ -1782,7 +1781,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>20</v>
       </c>
@@ -1817,7 +1816,7 @@
         <v>25.9</v>
       </c>
     </row>
-    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>17</v>
       </c>
@@ -1852,7 +1851,7 @@
         <v>8.3000000000000007</v>
       </c>
     </row>
-    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>17</v>
       </c>
@@ -1887,7 +1886,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>17</v>
       </c>
@@ -1922,7 +1921,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>11</v>
       </c>
@@ -1957,7 +1956,7 @@
         <v>8.1</v>
       </c>
     </row>
-    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>15</v>
       </c>
@@ -1992,7 +1991,7 @@
         <v>17.2</v>
       </c>
     </row>
-    <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>17</v>
       </c>
@@ -2027,7 +2026,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>20</v>
       </c>
@@ -2062,7 +2061,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>15</v>
       </c>
@@ -2097,7 +2096,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>17</v>
       </c>
@@ -2132,7 +2131,7 @@
         <v>8.1</v>
       </c>
     </row>
-    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>11</v>
       </c>
@@ -2167,7 +2166,7 @@
         <v>14.1</v>
       </c>
     </row>
-    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>24</v>
       </c>
@@ -2202,7 +2201,7 @@
         <v>14.9</v>
       </c>
     </row>
-    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>15</v>
       </c>
@@ -2237,7 +2236,7 @@
         <v>19.899999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>24</v>
       </c>
@@ -2272,7 +2271,7 @@
         <v>15.1</v>
       </c>
     </row>
-    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>15</v>
       </c>
@@ -2307,7 +2306,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>20</v>
       </c>
@@ -2342,7 +2341,7 @@
         <v>9.1999999999999993</v>
       </c>
     </row>
-    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>17</v>
       </c>
@@ -2377,7 +2376,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>20</v>
       </c>
@@ -2412,7 +2411,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>24</v>
       </c>
@@ -2447,7 +2446,7 @@
         <v>17.7</v>
       </c>
     </row>
-    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>17</v>
       </c>
@@ -2482,7 +2481,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>11</v>
       </c>
@@ -2517,7 +2516,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>17</v>
       </c>
@@ -2552,7 +2551,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>20</v>
       </c>
@@ -2587,7 +2586,7 @@
         <v>7.6</v>
       </c>
     </row>
-    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>15</v>
       </c>
@@ -2622,7 +2621,7 @@
         <v>8.9</v>
       </c>
     </row>
-    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>17</v>
       </c>
@@ -2657,7 +2656,7 @@
         <v>7.6</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>20</v>
       </c>
@@ -2692,7 +2691,7 @@
         <v>7.6</v>
       </c>
     </row>
-    <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>15</v>
       </c>
@@ -2727,7 +2726,7 @@
         <v>19.2</v>
       </c>
     </row>
-    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>24</v>
       </c>
@@ -2762,7 +2761,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="65" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>15</v>
       </c>
@@ -2797,7 +2796,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="66" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>24</v>
       </c>
@@ -2832,7 +2831,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>17</v>
       </c>
@@ -2867,7 +2866,7 @@
         <v>7.6</v>
       </c>
     </row>
-    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>15</v>
       </c>
@@ -2902,7 +2901,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>24</v>
       </c>
@@ -2937,7 +2936,7 @@
         <v>8.9</v>
       </c>
     </row>
-    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>24</v>
       </c>
@@ -2972,7 +2971,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="71" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>17</v>
       </c>
@@ -3007,7 +3006,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="72" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>20</v>
       </c>
@@ -3042,7 +3041,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="73" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>15</v>
       </c>
@@ -3077,7 +3076,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="74" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>24</v>
       </c>
@@ -3112,7 +3111,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="75" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>17</v>
       </c>
@@ -3147,7 +3146,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="76" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>17</v>
       </c>
@@ -3182,7 +3181,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>20</v>
       </c>
@@ -3217,7 +3216,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>11</v>
       </c>
@@ -3252,7 +3251,7 @@
         <v>8.8000000000000007</v>
       </c>
     </row>
-    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>24</v>
       </c>
@@ -3287,7 +3286,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>17</v>
       </c>
@@ -3322,7 +3321,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="81" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>15</v>
       </c>
@@ -3357,7 +3356,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="82" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>24</v>
       </c>
@@ -3392,7 +3391,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>11</v>
       </c>
@@ -3427,7 +3426,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>24</v>
       </c>
@@ -3462,7 +3461,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="85" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>24</v>
       </c>
@@ -3497,7 +3496,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>17</v>
       </c>
@@ -3532,7 +3531,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>20</v>
       </c>
@@ -3567,7 +3566,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>17</v>
       </c>
@@ -3602,7 +3601,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>24</v>
       </c>
@@ -3637,7 +3636,7 @@
         <v>6.3</v>
       </c>
     </row>
-    <row r="90" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>11</v>
       </c>
@@ -3672,7 +3671,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="91" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>17</v>
       </c>
@@ -3707,7 +3706,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="92" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>15</v>
       </c>
@@ -3742,7 +3741,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>15</v>
       </c>
@@ -3777,7 +3776,7 @@
         <v>15.9</v>
       </c>
     </row>
-    <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>24</v>
       </c>
@@ -3812,7 +3811,7 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="95" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>24</v>
       </c>
@@ -3847,7 +3846,7 @@
         <v>5.9</v>
       </c>
     </row>
-    <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>15</v>
       </c>
@@ -3882,7 +3881,7 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>17</v>
       </c>
@@ -3917,7 +3916,7 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="98" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>15</v>
       </c>
@@ -3952,7 +3951,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="99" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>15</v>
       </c>
@@ -3987,7 +3986,7 @@
         <v>8.1</v>
       </c>
     </row>
-    <row r="100" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>11</v>
       </c>
@@ -4022,7 +4021,7 @@
         <v>17.899999999999999</v>
       </c>
     </row>
-    <row r="101" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>20</v>
       </c>
@@ -4057,7 +4056,7 @@
         <v>15.9</v>
       </c>
     </row>
-    <row r="102" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>20</v>
       </c>
@@ -4092,7 +4091,7 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="103" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>20</v>
       </c>
@@ -4127,7 +4126,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="104" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>15</v>
       </c>
@@ -4162,7 +4161,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="105" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>11</v>
       </c>
@@ -4197,7 +4196,7 @@
         <v>14.8</v>
       </c>
     </row>
-    <row r="106" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>24</v>
       </c>
@@ -4232,7 +4231,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="107" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>15</v>
       </c>
@@ -4267,7 +4266,7 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="108" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>17</v>
       </c>
@@ -4302,7 +4301,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="109" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>11</v>
       </c>
@@ -4337,7 +4336,7 @@
         <v>18.8</v>
       </c>
     </row>
-    <row r="110" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>15</v>
       </c>
@@ -4372,7 +4371,7 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="111" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>20</v>
       </c>
@@ -4407,7 +4406,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="112" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>11</v>
       </c>
@@ -4442,7 +4441,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="113" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>15</v>
       </c>
@@ -4477,7 +4476,7 @@
         <v>19.899999999999999</v>
       </c>
     </row>
-    <row r="114" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>11</v>
       </c>
@@ -4512,7 +4511,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="115" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>24</v>
       </c>
@@ -4547,7 +4546,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="116" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>24</v>
       </c>
@@ -4582,7 +4581,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="117" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>15</v>
       </c>
@@ -4617,7 +4616,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="118" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>20</v>
       </c>
@@ -4652,7 +4651,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="119" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>11</v>
       </c>
@@ -4687,7 +4686,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="120" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>17</v>
       </c>
@@ -4722,7 +4721,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="121" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>17</v>
       </c>
@@ -4757,7 +4756,7 @@
         <v>18.899999999999999</v>
       </c>
     </row>
-    <row r="122" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>20</v>
       </c>
@@ -4792,7 +4791,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="123" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>17</v>
       </c>
@@ -4827,7 +4826,7 @@
         <v>14.7</v>
       </c>
     </row>
-    <row r="124" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>11</v>
       </c>
@@ -4862,7 +4861,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>24</v>
       </c>
@@ -4897,7 +4896,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="126" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>24</v>
       </c>
@@ -4932,7 +4931,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="127" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>17</v>
       </c>
@@ -4967,7 +4966,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="128" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>17</v>
       </c>
@@ -5002,7 +5001,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="129" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>24</v>
       </c>
@@ -5037,7 +5036,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="130" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>11</v>
       </c>
@@ -5072,7 +5071,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="131" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>20</v>
       </c>
@@ -5107,7 +5106,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>20</v>
       </c>
@@ -5142,7 +5141,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>11</v>
       </c>
@@ -5177,7 +5176,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="134" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>24</v>
       </c>
@@ -5212,7 +5211,7 @@
         <v>5.9</v>
       </c>
     </row>
-    <row r="135" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>17</v>
       </c>
@@ -5247,7 +5246,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="136" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>15</v>
       </c>
@@ -5282,7 +5281,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="137" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>15</v>
       </c>
@@ -5317,7 +5316,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="138" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>24</v>
       </c>
@@ -5352,7 +5351,7 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="139" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>11</v>
       </c>
@@ -5387,7 +5386,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="140" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>17</v>
       </c>
@@ -5422,7 +5421,7 @@
         <v>16.399999999999999</v>
       </c>
     </row>
-    <row r="141" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>15</v>
       </c>
@@ -5457,7 +5456,7 @@
         <v>17.399999999999999</v>
       </c>
     </row>
-    <row r="142" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>15</v>
       </c>
@@ -5492,7 +5491,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="143" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>17</v>
       </c>
@@ -5527,7 +5526,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="144" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>24</v>
       </c>
@@ -5562,7 +5561,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="145" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>15</v>
       </c>
@@ -5597,7 +5596,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="146" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>17</v>
       </c>
@@ -5632,7 +5631,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="147" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>15</v>
       </c>
@@ -5667,7 +5666,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="148" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>11</v>
       </c>
@@ -5702,7 +5701,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="149" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>11</v>
       </c>
@@ -5737,7 +5736,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="150" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>15</v>
       </c>
@@ -5772,7 +5771,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="151" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>11</v>
       </c>
@@ -5807,7 +5806,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="152" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>24</v>
       </c>
@@ -5842,7 +5841,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="153" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>15</v>
       </c>
@@ -5877,7 +5876,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="154" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>11</v>
       </c>
@@ -5912,7 +5911,7 @@
         <v>11.6</v>
       </c>
     </row>
-    <row r="155" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>11</v>
       </c>
@@ -5947,7 +5946,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="156" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>17</v>
       </c>
@@ -5982,7 +5981,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="157" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>11</v>
       </c>
@@ -6017,7 +6016,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="158" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>24</v>
       </c>
@@ -6052,7 +6051,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>11</v>
       </c>
@@ -6087,7 +6086,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="160" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>17</v>
       </c>
@@ -6122,7 +6121,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="161" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>24</v>
       </c>
@@ -6157,7 +6156,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="162" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>11</v>
       </c>
@@ -6192,7 +6191,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="163" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>20</v>
       </c>
@@ -6227,7 +6226,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="164" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>15</v>
       </c>
@@ -6262,7 +6261,7 @@
         <v>14.8</v>
       </c>
     </row>
-    <row r="165" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>11</v>
       </c>
@@ -6297,7 +6296,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="166" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>20</v>
       </c>
@@ -6332,7 +6331,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="167" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>15</v>
       </c>
@@ -6367,7 +6366,7 @@
         <v>16.399999999999999</v>
       </c>
     </row>
-    <row r="168" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>15</v>
       </c>
@@ -6402,7 +6401,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="169" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>15</v>
       </c>
@@ -6437,7 +6436,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="170" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>24</v>
       </c>
@@ -6472,7 +6471,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="171" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>17</v>
       </c>
@@ -6507,7 +6506,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="172" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>15</v>
       </c>
@@ -6542,7 +6541,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="173" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>15</v>
       </c>
@@ -6577,7 +6576,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="174" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>24</v>
       </c>
@@ -6612,7 +6611,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="175" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>20</v>
       </c>
@@ -6647,7 +6646,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="176" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>17</v>
       </c>
@@ -6682,7 +6681,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="177" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>15</v>
       </c>
@@ -6717,7 +6716,7 @@
         <v>15.2</v>
       </c>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>20</v>
       </c>
@@ -6752,7 +6751,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="179" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>11</v>
       </c>
@@ -6787,7 +6786,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="180" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>20</v>
       </c>
@@ -6822,7 +6821,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="181" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>17</v>
       </c>
@@ -6857,7 +6856,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="182" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>17</v>
       </c>
@@ -6892,7 +6891,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="183" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>15</v>
       </c>
@@ -6927,7 +6926,7 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="184" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
         <v>24</v>
       </c>
@@ -6962,7 +6961,7 @@
         <v>11.3</v>
       </c>
     </row>
-    <row r="185" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>17</v>
       </c>
@@ -6997,7 +6996,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="186" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>15</v>
       </c>
@@ -7032,7 +7031,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="187" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>17</v>
       </c>
@@ -7067,7 +7066,7 @@
         <v>19.399999999999999</v>
       </c>
     </row>
-    <row r="188" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>20</v>
       </c>
@@ -7102,7 +7101,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="189" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>15</v>
       </c>
@@ -7137,7 +7136,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="190" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>11</v>
       </c>
@@ -7172,7 +7171,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="191" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>24</v>
       </c>
@@ -7207,7 +7206,7 @@
         <v>19.3</v>
       </c>
     </row>
-    <row r="192" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>20</v>
       </c>
@@ -7242,7 +7241,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="193" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>11</v>
       </c>
@@ -7277,7 +7276,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="194" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>15</v>
       </c>
@@ -7312,7 +7311,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="195" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>24</v>
       </c>
@@ -7347,7 +7346,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>11</v>
       </c>
@@ -7382,7 +7381,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="197" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>15</v>
       </c>
@@ -7417,7 +7416,7 @@
         <v>19.3</v>
       </c>
     </row>
-    <row r="198" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>17</v>
       </c>
@@ -7452,7 +7451,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="199" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>24</v>
       </c>
@@ -7487,7 +7486,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="200" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
         <v>17</v>
       </c>
@@ -7522,7 +7521,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="201" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
         <v>15</v>
       </c>
@@ -7557,7 +7556,7 @@
         <v>19.399999999999999</v>
       </c>
     </row>
-    <row r="202" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
         <v>11</v>
       </c>
@@ -7592,7 +7591,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="203" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>15</v>
       </c>
@@ -7627,7 +7626,7 @@
         <v>18.899999999999999</v>
       </c>
     </row>
-    <row r="204" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>24</v>
       </c>
@@ -7662,7 +7661,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="205" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>17</v>
       </c>
@@ -7697,7 +7696,7 @@
         <v>15.4</v>
       </c>
     </row>
-    <row r="206" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>24</v>
       </c>
@@ -7732,7 +7731,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="207" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>17</v>
       </c>
@@ -7767,7 +7766,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="208" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>24</v>
       </c>
@@ -7802,7 +7801,7 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="209" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>20</v>
       </c>
@@ -7837,7 +7836,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="210" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>17</v>
       </c>
@@ -7872,7 +7871,7 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="211" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>20</v>
       </c>
@@ -7907,7 +7906,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>20</v>
       </c>
@@ -7942,7 +7941,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="213" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>15</v>
       </c>
@@ -7977,7 +7976,7 @@
         <v>17.2</v>
       </c>
     </row>
-    <row r="214" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>15</v>
       </c>
@@ -8012,7 +8011,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="215" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>20</v>
       </c>
@@ -8047,7 +8046,7 @@
         <v>9.4</v>
       </c>
     </row>
-    <row r="216" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>15</v>
       </c>
@@ -8082,7 +8081,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="217" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>20</v>
       </c>
@@ -8117,7 +8116,7 @@
         <v>19.3</v>
       </c>
     </row>
-    <row r="218" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>11</v>
       </c>
@@ -8152,7 +8151,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="219" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>20</v>
       </c>
@@ -8187,7 +8186,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="220" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>20</v>
       </c>
@@ -8222,7 +8221,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="221" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>15</v>
       </c>
@@ -8257,7 +8256,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="222" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>11</v>
       </c>
@@ -8292,7 +8291,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="223" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>15</v>
       </c>
@@ -8327,7 +8326,7 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="224" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
         <v>17</v>
       </c>
@@ -8362,7 +8361,7 @@
         <v>19.2</v>
       </c>
     </row>
-    <row r="225" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
         <v>17</v>
       </c>
@@ -8397,7 +8396,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="226" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>17</v>
       </c>
@@ -8432,7 +8431,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="227" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>15</v>
       </c>
@@ -8467,7 +8466,7 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="228" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>17</v>
       </c>
@@ -8502,7 +8501,7 @@
         <v>16.399999999999999</v>
       </c>
     </row>
-    <row r="229" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>11</v>
       </c>
@@ -8537,7 +8536,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="230" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>20</v>
       </c>
@@ -8572,7 +8571,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="231" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>11</v>
       </c>
@@ -8607,7 +8606,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="232" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
         <v>11</v>
       </c>
@@ -8642,7 +8641,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="233" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
         <v>11</v>
       </c>
@@ -8677,7 +8676,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="234" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
         <v>20</v>
       </c>
@@ -8712,7 +8711,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="235" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
         <v>17</v>
       </c>
@@ -8747,7 +8746,7 @@
         <v>8.8000000000000007</v>
       </c>
     </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
         <v>15</v>
       </c>
@@ -8782,7 +8781,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="237" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
         <v>24</v>
       </c>
@@ -8817,7 +8816,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="238" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
         <v>15</v>
       </c>
@@ -8852,7 +8851,7 @@
         <v>17.399999999999999</v>
       </c>
     </row>
-    <row r="239" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
         <v>11</v>
       </c>
@@ -8887,7 +8886,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="240" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
         <v>15</v>
       </c>
@@ -8922,7 +8921,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="241" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
         <v>15</v>
       </c>
@@ -8957,7 +8956,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="242" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
         <v>17</v>
       </c>
@@ -8992,7 +8991,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="243" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
         <v>24</v>
       </c>
@@ -9027,7 +9026,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="244" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
         <v>11</v>
       </c>
@@ -9062,7 +9061,7 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="245" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
         <v>17</v>
       </c>
@@ -9097,7 +9096,7 @@
         <v>11.6</v>
       </c>
     </row>
-    <row r="246" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
         <v>15</v>
       </c>
@@ -9132,7 +9131,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="247" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
         <v>20</v>
       </c>
@@ -9167,7 +9166,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="248" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
         <v>24</v>
       </c>
@@ -9202,7 +9201,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="249" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
         <v>15</v>
       </c>
@@ -9237,7 +9236,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="250" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
         <v>20</v>
       </c>
@@ -9272,7 +9271,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="251" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
         <v>24</v>
       </c>
@@ -9307,7 +9306,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="252" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
         <v>17</v>
       </c>
@@ -9342,7 +9341,7 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="253" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
         <v>24</v>
       </c>
@@ -9377,7 +9376,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="254" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
         <v>17</v>
       </c>
@@ -9412,7 +9411,7 @@
         <v>15.2</v>
       </c>
     </row>
-    <row r="255" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
         <v>20</v>
       </c>
@@ -9447,7 +9446,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="256" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
         <v>20</v>
       </c>
@@ -9482,7 +9481,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="257" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
         <v>15</v>
       </c>
@@ -9517,7 +9516,7 @@
         <v>9.9</v>
       </c>
     </row>
-    <row r="258" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
         <v>24</v>
       </c>
@@ -9552,7 +9551,7 @@
         <v>15.9</v>
       </c>
     </row>
-    <row r="259" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
         <v>17</v>
       </c>
@@ -9587,7 +9586,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="260" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
         <v>15</v>
       </c>
@@ -9622,7 +9621,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="261" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
         <v>20</v>
       </c>
@@ -9657,7 +9656,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="262" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
         <v>11</v>
       </c>
@@ -9692,7 +9691,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="263" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
         <v>17</v>
       </c>
@@ -9727,7 +9726,7 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="264" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
         <v>11</v>
       </c>
@@ -9762,7 +9761,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="265" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
         <v>17</v>
       </c>
@@ -9797,7 +9796,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="266" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
         <v>11</v>
       </c>
@@ -9832,7 +9831,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="267" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
         <v>24</v>
       </c>
@@ -9867,7 +9866,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="268" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
         <v>15</v>
       </c>
@@ -9902,7 +9901,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="269" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
         <v>15</v>
       </c>
@@ -9937,7 +9936,7 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="270" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
         <v>15</v>
       </c>
@@ -9972,7 +9971,7 @@
         <v>17.399999999999999</v>
       </c>
     </row>
-    <row r="271" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
         <v>24</v>
       </c>
@@ -10007,7 +10006,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="272" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
         <v>20</v>
       </c>
@@ -10042,7 +10041,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="273" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
         <v>20</v>
       </c>
@@ -10077,7 +10076,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="274" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
         <v>17</v>
       </c>
@@ -10112,7 +10111,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="275" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
         <v>24</v>
       </c>
@@ -10147,7 +10146,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="276" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
         <v>24</v>
       </c>
@@ -10182,7 +10181,7 @@
         <v>14.8</v>
       </c>
     </row>
-    <row r="277" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
         <v>15</v>
       </c>
@@ -10217,7 +10216,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="278" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
         <v>11</v>
       </c>
@@ -10252,7 +10251,7 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="279" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
         <v>17</v>
       </c>
@@ -10287,7 +10286,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="280" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
         <v>17</v>
       </c>
@@ -10322,7 +10321,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="281" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
         <v>20</v>
       </c>
@@ -10357,7 +10356,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="282" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
         <v>15</v>
       </c>
@@ -10392,7 +10391,7 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="283" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
         <v>15</v>
       </c>
@@ -10427,7 +10426,7 @@
         <v>17.8</v>
       </c>
     </row>
-    <row r="284" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
         <v>11</v>
       </c>
@@ -10462,7 +10461,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="285" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
         <v>11</v>
       </c>
@@ -10497,7 +10496,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="286" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
         <v>17</v>
       </c>
@@ -10532,7 +10531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="287" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
         <v>24</v>
       </c>
@@ -10567,7 +10566,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="288" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
         <v>11</v>
       </c>
@@ -10602,7 +10601,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="289" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
         <v>17</v>
       </c>
@@ -10637,7 +10636,7 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="290" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
         <v>20</v>
       </c>
@@ -10672,7 +10671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="291" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
         <v>11</v>
       </c>
@@ -10707,7 +10706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="292" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A292" s="2"/>
       <c r="B292" s="2"/>
       <c r="C292" s="2"/>
@@ -10720,7 +10719,7 @@
       <c r="J292" s="2"/>
       <c r="K292" s="2"/>
     </row>
-    <row r="293" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A293" s="2"/>
       <c r="B293" s="2"/>
       <c r="C293" s="2"/>
@@ -10733,7 +10732,7 @@
       <c r="J293" s="2"/>
       <c r="K293" s="2"/>
     </row>
-    <row r="294" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A294" s="4" t="s">
         <v>28</v>
       </c>
@@ -10748,7 +10747,7 @@
       <c r="J294" s="2"/>
       <c r="K294" s="2"/>
     </row>
-    <row r="295" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A295" s="5" t="s">
         <v>29</v>
       </c>
@@ -10763,7 +10762,7 @@
       <c r="J295" s="2"/>
       <c r="K295" s="2"/>
     </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A296" s="2"/>
       <c r="B296" s="2"/>
       <c r="C296" s="2"/>
@@ -10776,7 +10775,7 @@
       <c r="J296" s="2"/>
       <c r="K296" s="2"/>
     </row>
-    <row r="297" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A297" s="2"/>
       <c r="B297" s="2"/>
       <c r="C297" s="2"/>
@@ -10789,7 +10788,7 @@
       <c r="J297" s="2"/>
       <c r="K297" s="2"/>
     </row>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A298" s="2"/>
       <c r="B298" s="2"/>
       <c r="C298" s="2"/>
@@ -10802,7 +10801,7 @@
       <c r="J298" s="2"/>
       <c r="K298" s="2"/>
     </row>
-    <row r="299" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A299" s="2"/>
       <c r="B299" s="2"/>
       <c r="C299" s="2"/>
@@ -10815,7 +10814,7 @@
       <c r="J299" s="2"/>
       <c r="K299" s="2"/>
     </row>
-    <row r="300" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A300" s="2"/>
       <c r="B300" s="2"/>
       <c r="C300" s="2"/>
@@ -10828,7 +10827,7 @@
       <c r="J300" s="2"/>
       <c r="K300" s="2"/>
     </row>
-    <row r="301" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A301" s="2"/>
       <c r="B301" s="2"/>
       <c r="C301" s="2"/>
@@ -10843,16 +10842,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:K291" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Orgânico"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="2">
-      <filters>
-        <filter val="Industrial"/>
-      </filters>
-    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A9:K279">
       <sortCondition descending="1" ref="K1:K291"/>
     </sortState>

--- a/tables/Solid_waste_pt.xlsx
+++ b/tables/Solid_waste_pt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1848e9536f9f8e2e/Documentos/GitHub/Solid_Waste_Data_Analysis_Study/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{EEE2A7F0-8F4E-4449-8D35-44DBE395A750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A8D3885-5B3D-4E8D-B959-00BCA51E3F44}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="13_ncr:1_{EEE2A7F0-8F4E-4449-8D35-44DBE395A750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D667B06-42E3-4672-8011-B79AD987D9B9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -219,6 +219,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -510,15 +514,15 @@
   <dimension ref="A1:K301"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.42578125" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="14.7109375" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="23.42578125" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
     <col min="4" max="5" width="20" customWidth="1"/>
     <col min="6" max="6" width="25" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
     <col min="8" max="8" width="26" customWidth="1"/>
-    <col min="9" max="9" width="33" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="29" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="33" customWidth="1"/>
+    <col min="10" max="10" width="29" customWidth="1"/>
     <col min="11" max="11" width="24" customWidth="1"/>
   </cols>
   <sheetData>

--- a/tables/Solid_waste_pt.xlsx
+++ b/tables/Solid_waste_pt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1848e9536f9f8e2e/Documentos/GitHub/Solid_Waste_Data_Analysis_Study/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="13_ncr:1_{EEE2A7F0-8F4E-4449-8D35-44DBE395A750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D667B06-42E3-4672-8011-B79AD987D9B9}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="13_ncr:1_{EEE2A7F0-8F4E-4449-8D35-44DBE395A750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E3CB306-3C71-404A-A193-2EFB3B4BEA87}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1173" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1171" uniqueCount="28">
   <si>
     <t>Regiao_Coleta</t>
   </si>
@@ -121,12 +121,6 @@
   <si>
     <t>Serviços de Saúde</t>
   </si>
-  <si>
-    <t>Varíaveis qualitativas</t>
-  </si>
-  <si>
-    <t>Varíaveis quantitativas</t>
-  </si>
 </sst>
 </file>
 
@@ -188,7 +182,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -197,13 +191,10 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -510,7 +501,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:K301"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -561,7 +551,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>15</v>
       </c>
@@ -596,7 +586,7 @@
         <v>19.2</v>
       </c>
     </row>
-    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -631,7 +621,7 @@
         <v>8.1</v>
       </c>
     </row>
-    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
@@ -666,7 +656,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>17</v>
       </c>
@@ -701,7 +691,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>20</v>
       </c>
@@ -736,7 +726,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>15</v>
       </c>
@@ -806,7 +796,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
@@ -841,7 +831,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
@@ -876,7 +866,7 @@
         <v>9.3000000000000007</v>
       </c>
     </row>
-    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>24</v>
       </c>
@@ -911,7 +901,7 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>15</v>
       </c>
@@ -946,7 +936,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>15</v>
       </c>
@@ -981,7 +971,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>17</v>
       </c>
@@ -1016,7 +1006,7 @@
         <v>9.3000000000000007</v>
       </c>
     </row>
-    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>11</v>
       </c>
@@ -1051,7 +1041,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>17</v>
       </c>
@@ -1086,7 +1076,7 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>11</v>
       </c>
@@ -1121,7 +1111,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>15</v>
       </c>
@@ -1191,7 +1181,7 @@
         <v>9.6999999999999993</v>
       </c>
     </row>
-    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>15</v>
       </c>
@@ -1226,7 +1216,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>17</v>
       </c>
@@ -1261,7 +1251,7 @@
         <v>8.1</v>
       </c>
     </row>
-    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>20</v>
       </c>
@@ -1296,7 +1286,7 @@
         <v>9.3000000000000007</v>
       </c>
     </row>
-    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>20</v>
       </c>
@@ -1331,7 +1321,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>20</v>
       </c>
@@ -1366,7 +1356,7 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>20</v>
       </c>
@@ -1401,7 +1391,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>17</v>
       </c>
@@ -1436,7 +1426,7 @@
         <v>9.4</v>
       </c>
     </row>
-    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>20</v>
       </c>
@@ -1471,7 +1461,7 @@
         <v>7.6</v>
       </c>
     </row>
-    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>15</v>
       </c>
@@ -1506,7 +1496,7 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>17</v>
       </c>
@@ -1541,7 +1531,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>24</v>
       </c>
@@ -1611,7 +1601,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>20</v>
       </c>
@@ -1646,7 +1636,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>17</v>
       </c>
@@ -1716,7 +1706,7 @@
         <v>5.9</v>
       </c>
     </row>
-    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>11</v>
       </c>
@@ -1751,7 +1741,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>17</v>
       </c>
@@ -1786,7 +1776,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>20</v>
       </c>
@@ -1821,7 +1811,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>11</v>
       </c>
@@ -1856,7 +1846,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>24</v>
       </c>
@@ -1891,7 +1881,7 @@
         <v>11.9</v>
       </c>
     </row>
-    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>20</v>
       </c>
@@ -1926,7 +1916,7 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>24</v>
       </c>
@@ -1961,7 +1951,7 @@
         <v>9.1</v>
       </c>
     </row>
-    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>11</v>
       </c>
@@ -1996,7 +1986,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>17</v>
       </c>
@@ -2031,7 +2021,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>11</v>
       </c>
@@ -2066,7 +2056,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>20</v>
       </c>
@@ -2101,7 +2091,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>20</v>
       </c>
@@ -2136,7 +2126,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>15</v>
       </c>
@@ -2171,7 +2161,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>20</v>
       </c>
@@ -2206,7 +2196,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>17</v>
       </c>
@@ -2241,7 +2231,7 @@
         <v>8.3000000000000007</v>
       </c>
     </row>
-    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>24</v>
       </c>
@@ -2276,7 +2266,7 @@
         <v>15.1</v>
       </c>
     </row>
-    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>15</v>
       </c>
@@ -2311,7 +2301,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>20</v>
       </c>
@@ -2346,7 +2336,7 @@
         <v>9.1999999999999993</v>
       </c>
     </row>
-    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>24</v>
       </c>
@@ -2381,7 +2371,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>15</v>
       </c>
@@ -2416,7 +2406,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>24</v>
       </c>
@@ -2451,7 +2441,7 @@
         <v>17.7</v>
       </c>
     </row>
-    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>17</v>
       </c>
@@ -2486,7 +2476,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>11</v>
       </c>
@@ -2556,7 +2546,7 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>24</v>
       </c>
@@ -2591,7 +2581,7 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>15</v>
       </c>
@@ -2626,7 +2616,7 @@
         <v>8.9</v>
       </c>
     </row>
-    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>24</v>
       </c>
@@ -2661,7 +2651,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>20</v>
       </c>
@@ -2696,7 +2686,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>15</v>
       </c>
@@ -2731,7 +2721,7 @@
         <v>19.2</v>
       </c>
     </row>
-    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>24</v>
       </c>
@@ -2766,7 +2756,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="65" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>15</v>
       </c>
@@ -2801,7 +2791,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="66" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>24</v>
       </c>
@@ -2836,7 +2826,7 @@
         <v>8.8000000000000007</v>
       </c>
     </row>
-    <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>15</v>
       </c>
@@ -2871,7 +2861,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>17</v>
       </c>
@@ -2906,7 +2896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>24</v>
       </c>
@@ -2941,7 +2931,7 @@
         <v>8.9</v>
       </c>
     </row>
-    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>15</v>
       </c>
@@ -2976,7 +2966,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="71" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>20</v>
       </c>
@@ -3011,7 +3001,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="72" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>24</v>
       </c>
@@ -3046,7 +3036,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="73" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>15</v>
       </c>
@@ -3081,7 +3071,7 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="74" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>24</v>
       </c>
@@ -3116,7 +3106,7 @@
         <v>6.3</v>
       </c>
     </row>
-    <row r="75" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>15</v>
       </c>
@@ -3151,7 +3141,7 @@
         <v>9.1</v>
       </c>
     </row>
-    <row r="76" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>17</v>
       </c>
@@ -3186,7 +3176,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>20</v>
       </c>
@@ -3221,7 +3211,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>11</v>
       </c>
@@ -3256,7 +3246,7 @@
         <v>8.8000000000000007</v>
       </c>
     </row>
-    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>24</v>
       </c>
@@ -3291,7 +3281,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>11</v>
       </c>
@@ -3326,7 +3316,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="81" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>11</v>
       </c>
@@ -3361,7 +3351,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="82" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>17</v>
       </c>
@@ -3396,7 +3386,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>11</v>
       </c>
@@ -3431,7 +3421,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>24</v>
       </c>
@@ -3466,7 +3456,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="85" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>24</v>
       </c>
@@ -3501,7 +3491,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>17</v>
       </c>
@@ -3536,7 +3526,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>24</v>
       </c>
@@ -3571,7 +3561,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="88" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>20</v>
       </c>
@@ -3606,7 +3596,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>20</v>
       </c>
@@ -3676,7 +3666,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="91" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>17</v>
       </c>
@@ -3711,7 +3701,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="92" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>15</v>
       </c>
@@ -3746,7 +3736,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>15</v>
       </c>
@@ -3781,7 +3771,7 @@
         <v>15.9</v>
       </c>
     </row>
-    <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>20</v>
       </c>
@@ -3816,7 +3806,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="95" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>17</v>
       </c>
@@ -3851,7 +3841,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>15</v>
       </c>
@@ -3886,7 +3876,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="97" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>17</v>
       </c>
@@ -3921,7 +3911,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="98" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>17</v>
       </c>
@@ -3956,7 +3946,7 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="99" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>15</v>
       </c>
@@ -3991,7 +3981,7 @@
         <v>8.1</v>
       </c>
     </row>
-    <row r="100" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>11</v>
       </c>
@@ -4026,7 +4016,7 @@
         <v>17.899999999999999</v>
       </c>
     </row>
-    <row r="101" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>20</v>
       </c>
@@ -4096,7 +4086,7 @@
         <v>8.8000000000000007</v>
       </c>
     </row>
-    <row r="103" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>20</v>
       </c>
@@ -4131,7 +4121,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="104" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>15</v>
       </c>
@@ -4166,7 +4156,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="105" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>11</v>
       </c>
@@ -4236,7 +4226,7 @@
         <v>7.6</v>
       </c>
     </row>
-    <row r="107" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>15</v>
       </c>
@@ -4271,7 +4261,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="108" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>17</v>
       </c>
@@ -4306,7 +4296,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="109" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>11</v>
       </c>
@@ -4411,7 +4401,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="112" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>11</v>
       </c>
@@ -4446,7 +4436,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="113" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>15</v>
       </c>
@@ -4481,7 +4471,7 @@
         <v>19.899999999999999</v>
       </c>
     </row>
-    <row r="114" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>11</v>
       </c>
@@ -4516,7 +4506,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="115" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>24</v>
       </c>
@@ -4551,7 +4541,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="116" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>24</v>
       </c>
@@ -4586,7 +4576,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="117" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>15</v>
       </c>
@@ -4621,7 +4611,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="118" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>20</v>
       </c>
@@ -4691,7 +4681,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="120" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>17</v>
       </c>
@@ -4726,7 +4716,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="121" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>24</v>
       </c>
@@ -4761,7 +4751,7 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="122" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>20</v>
       </c>
@@ -4796,7 +4786,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="123" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>17</v>
       </c>
@@ -4866,7 +4856,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="125" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>17</v>
       </c>
@@ -4901,7 +4891,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="126" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>20</v>
       </c>
@@ -4936,7 +4926,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="127" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>11</v>
       </c>
@@ -4971,7 +4961,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="128" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>11</v>
       </c>
@@ -5006,7 +4996,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="129" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>20</v>
       </c>
@@ -5041,7 +5031,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="130" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>11</v>
       </c>
@@ -5076,7 +5066,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="131" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>17</v>
       </c>
@@ -5111,7 +5101,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="132" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>20</v>
       </c>
@@ -5146,7 +5136,7 @@
         <v>7.6</v>
       </c>
     </row>
-    <row r="133" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>17</v>
       </c>
@@ -5181,7 +5171,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="134" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>24</v>
       </c>
@@ -5216,7 +5206,7 @@
         <v>5.9</v>
       </c>
     </row>
-    <row r="135" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>17</v>
       </c>
@@ -5286,7 +5276,7 @@
         <v>9.6999999999999993</v>
       </c>
     </row>
-    <row r="137" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>20</v>
       </c>
@@ -5321,7 +5311,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="138" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>24</v>
       </c>
@@ -5356,7 +5346,7 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="139" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>11</v>
       </c>
@@ -5426,7 +5416,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="141" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>11</v>
       </c>
@@ -5461,7 +5451,7 @@
         <v>9.3000000000000007</v>
       </c>
     </row>
-    <row r="142" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>11</v>
       </c>
@@ -5496,7 +5486,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="143" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>11</v>
       </c>
@@ -5531,7 +5521,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="144" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>17</v>
       </c>
@@ -5566,7 +5556,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="145" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>24</v>
       </c>
@@ -5601,7 +5591,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="146" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>15</v>
       </c>
@@ -5636,7 +5626,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="147" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>20</v>
       </c>
@@ -5671,7 +5661,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="148" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>11</v>
       </c>
@@ -5706,7 +5696,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="149" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>11</v>
       </c>
@@ -5741,7 +5731,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="150" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>15</v>
       </c>
@@ -5776,7 +5766,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="151" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>11</v>
       </c>
@@ -5846,7 +5836,7 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="153" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>15</v>
       </c>
@@ -5881,7 +5871,7 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="154" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>15</v>
       </c>
@@ -5916,7 +5906,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="155" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>24</v>
       </c>
@@ -5951,7 +5941,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="156" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>17</v>
       </c>
@@ -5986,7 +5976,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="157" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>17</v>
       </c>
@@ -6056,7 +6046,7 @@
         <v>16.399999999999999</v>
       </c>
     </row>
-    <row r="159" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>11</v>
       </c>
@@ -6091,7 +6081,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="160" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>17</v>
       </c>
@@ -6126,7 +6116,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="161" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>24</v>
       </c>
@@ -6161,7 +6151,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="162" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>11</v>
       </c>
@@ -6196,7 +6186,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="163" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>15</v>
       </c>
@@ -6231,7 +6221,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="164" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>20</v>
       </c>
@@ -6301,7 +6291,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="166" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>24</v>
       </c>
@@ -6336,7 +6326,7 @@
         <v>11.3</v>
       </c>
     </row>
-    <row r="167" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>17</v>
       </c>
@@ -6371,7 +6361,7 @@
         <v>11.6</v>
       </c>
     </row>
-    <row r="168" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>15</v>
       </c>
@@ -6406,7 +6396,7 @@
         <v>17.399999999999999</v>
       </c>
     </row>
-    <row r="169" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>17</v>
       </c>
@@ -6441,7 +6431,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="170" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>17</v>
       </c>
@@ -6476,7 +6466,7 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="171" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>11</v>
       </c>
@@ -6511,7 +6501,7 @@
         <v>11.6</v>
       </c>
     </row>
-    <row r="172" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>24</v>
       </c>
@@ -6546,7 +6536,7 @@
         <v>8.8000000000000007</v>
       </c>
     </row>
-    <row r="173" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>17</v>
       </c>
@@ -6581,7 +6571,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="174" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>24</v>
       </c>
@@ -6616,7 +6606,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="175" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>17</v>
       </c>
@@ -6651,7 +6641,7 @@
         <v>8.8000000000000007</v>
       </c>
     </row>
-    <row r="176" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>24</v>
       </c>
@@ -6686,7 +6676,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="177" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>20</v>
       </c>
@@ -6721,7 +6711,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="178" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>15</v>
       </c>
@@ -6756,7 +6746,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="179" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>11</v>
       </c>
@@ -6791,7 +6781,7 @@
         <v>14.1</v>
       </c>
     </row>
-    <row r="180" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>20</v>
       </c>
@@ -6826,7 +6816,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="181" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>17</v>
       </c>
@@ -6861,7 +6851,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="182" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>15</v>
       </c>
@@ -6896,7 +6886,7 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="183" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>20</v>
       </c>
@@ -6931,7 +6921,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="184" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
         <v>24</v>
       </c>
@@ -6966,7 +6956,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="185" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>24</v>
       </c>
@@ -7001,7 +6991,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="186" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>15</v>
       </c>
@@ -7036,7 +7026,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="187" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>24</v>
       </c>
@@ -7071,7 +7061,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="188" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>15</v>
       </c>
@@ -7106,7 +7096,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="189" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>17</v>
       </c>
@@ -7141,7 +7131,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="190" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>17</v>
       </c>
@@ -7211,7 +7201,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="192" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>20</v>
       </c>
@@ -7246,7 +7236,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="193" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>17</v>
       </c>
@@ -7281,7 +7271,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="194" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>15</v>
       </c>
@@ -7316,7 +7306,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="195" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>17</v>
       </c>
@@ -7351,7 +7341,7 @@
         <v>19.2</v>
       </c>
     </row>
-    <row r="196" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>20</v>
       </c>
@@ -7386,7 +7376,7 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="197" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>20</v>
       </c>
@@ -7421,7 +7411,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="198" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>11</v>
       </c>
@@ -7456,7 +7446,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="199" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>11</v>
       </c>
@@ -7491,7 +7481,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="200" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
         <v>17</v>
       </c>
@@ -7526,7 +7516,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="201" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
         <v>15</v>
       </c>
@@ -7561,7 +7551,7 @@
         <v>18.899999999999999</v>
       </c>
     </row>
-    <row r="202" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
         <v>17</v>
       </c>
@@ -7596,7 +7586,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="203" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>24</v>
       </c>
@@ -7631,7 +7621,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="204" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>15</v>
       </c>
@@ -7666,7 +7656,7 @@
         <v>15.2</v>
       </c>
     </row>
-    <row r="205" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>24</v>
       </c>
@@ -7701,7 +7691,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="206" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>17</v>
       </c>
@@ -7736,7 +7726,7 @@
         <v>19.2</v>
       </c>
     </row>
-    <row r="207" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>15</v>
       </c>
@@ -7771,7 +7761,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="208" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>17</v>
       </c>
@@ -7806,7 +7796,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="209" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>24</v>
       </c>
@@ -7841,7 +7831,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="210" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>24</v>
       </c>
@@ -7876,11 +7866,11 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="211" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B211" s="6" t="s">
+      <c r="B211" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C211" s="2" t="s">
@@ -7911,7 +7901,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="212" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>20</v>
       </c>
@@ -7946,7 +7936,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="213" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>24</v>
       </c>
@@ -7981,7 +7971,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="214" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>15</v>
       </c>
@@ -8016,7 +8006,7 @@
         <v>19.3</v>
       </c>
     </row>
-    <row r="215" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>24</v>
       </c>
@@ -8051,7 +8041,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="216" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>15</v>
       </c>
@@ -8086,7 +8076,7 @@
         <v>19.399999999999999</v>
       </c>
     </row>
-    <row r="217" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>15</v>
       </c>
@@ -8156,7 +8146,7 @@
         <v>15.2</v>
       </c>
     </row>
-    <row r="219" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>11</v>
       </c>
@@ -8191,7 +8181,7 @@
         <v>19.2</v>
       </c>
     </row>
-    <row r="220" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>17</v>
       </c>
@@ -8226,7 +8216,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="221" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>17</v>
       </c>
@@ -8296,7 +8286,7 @@
         <v>17.2</v>
       </c>
     </row>
-    <row r="223" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>24</v>
       </c>
@@ -8331,7 +8321,7 @@
         <v>14.9</v>
       </c>
     </row>
-    <row r="224" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
         <v>11</v>
       </c>
@@ -8366,7 +8356,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="225" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
         <v>15</v>
       </c>
@@ -8401,7 +8391,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="226" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>17</v>
       </c>
@@ -8436,7 +8426,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="227" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>20</v>
       </c>
@@ -8471,7 +8461,7 @@
         <v>25.9</v>
       </c>
     </row>
-    <row r="228" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>17</v>
       </c>
@@ -8506,7 +8496,7 @@
         <v>16.399999999999999</v>
       </c>
     </row>
-    <row r="229" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>24</v>
       </c>
@@ -8541,7 +8531,7 @@
         <v>14.8</v>
       </c>
     </row>
-    <row r="230" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>11</v>
       </c>
@@ -8576,7 +8566,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="231" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>15</v>
       </c>
@@ -8611,7 +8601,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="232" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
         <v>11</v>
       </c>
@@ -8681,7 +8671,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="234" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
         <v>15</v>
       </c>
@@ -8716,7 +8706,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="235" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
         <v>20</v>
       </c>
@@ -8751,7 +8741,7 @@
         <v>19.3</v>
       </c>
     </row>
-    <row r="236" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
         <v>24</v>
       </c>
@@ -8786,7 +8776,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="237" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
         <v>24</v>
       </c>
@@ -8821,7 +8811,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="238" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
         <v>11</v>
       </c>
@@ -8891,7 +8881,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="240" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
         <v>11</v>
       </c>
@@ -8926,7 +8916,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="241" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
         <v>15</v>
       </c>
@@ -8961,7 +8951,7 @@
         <v>17.399999999999999</v>
       </c>
     </row>
-    <row r="242" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
         <v>17</v>
       </c>
@@ -8996,7 +8986,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="243" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
         <v>20</v>
       </c>
@@ -9031,7 +9021,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="244" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
         <v>17</v>
       </c>
@@ -9066,7 +9056,7 @@
         <v>19.399999999999999</v>
       </c>
     </row>
-    <row r="245" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
         <v>15</v>
       </c>
@@ -9101,7 +9091,7 @@
         <v>16.399999999999999</v>
       </c>
     </row>
-    <row r="246" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
         <v>15</v>
       </c>
@@ -9136,7 +9126,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="247" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
         <v>17</v>
       </c>
@@ -9171,7 +9161,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="248" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
         <v>15</v>
       </c>
@@ -9206,7 +9196,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="249" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
         <v>17</v>
       </c>
@@ -9241,7 +9231,7 @@
         <v>18.899999999999999</v>
       </c>
     </row>
-    <row r="250" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
         <v>15</v>
       </c>
@@ -9311,7 +9301,7 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="252" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
         <v>20</v>
       </c>
@@ -9346,7 +9336,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="253" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
         <v>17</v>
       </c>
@@ -9416,7 +9406,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="255" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
         <v>20</v>
       </c>
@@ -9451,7 +9441,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="256" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
         <v>24</v>
       </c>
@@ -9486,7 +9476,7 @@
         <v>19.3</v>
       </c>
     </row>
-    <row r="257" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
         <v>15</v>
       </c>
@@ -9521,7 +9511,7 @@
         <v>9.9</v>
       </c>
     </row>
-    <row r="258" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
         <v>20</v>
       </c>
@@ -9591,7 +9581,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="260" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
         <v>24</v>
       </c>
@@ -9626,7 +9616,7 @@
         <v>17.399999999999999</v>
       </c>
     </row>
-    <row r="261" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
         <v>24</v>
       </c>
@@ -9661,7 +9651,7 @@
         <v>15.9</v>
       </c>
     </row>
-    <row r="262" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
         <v>11</v>
       </c>
@@ -9696,7 +9686,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="263" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
         <v>15</v>
       </c>
@@ -9731,7 +9721,7 @@
         <v>19.899999999999999</v>
       </c>
     </row>
-    <row r="264" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
         <v>24</v>
       </c>
@@ -9766,7 +9756,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="265" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
         <v>24</v>
       </c>
@@ -9801,7 +9791,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="266" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
         <v>17</v>
       </c>
@@ -9836,7 +9826,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="267" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
         <v>11</v>
       </c>
@@ -9871,7 +9861,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="268" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
         <v>11</v>
       </c>
@@ -9906,7 +9896,7 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="269" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
         <v>15</v>
       </c>
@@ -9941,7 +9931,7 @@
         <v>17.399999999999999</v>
       </c>
     </row>
-    <row r="270" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
         <v>15</v>
       </c>
@@ -9976,7 +9966,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="271" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
         <v>17</v>
       </c>
@@ -10011,7 +10001,7 @@
         <v>17.7</v>
       </c>
     </row>
-    <row r="272" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
         <v>20</v>
       </c>
@@ -10046,7 +10036,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="273" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
         <v>15</v>
       </c>
@@ -10081,7 +10071,7 @@
         <v>17.2</v>
       </c>
     </row>
-    <row r="274" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
         <v>17</v>
       </c>
@@ -10116,7 +10106,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="275" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
         <v>15</v>
       </c>
@@ -10151,7 +10141,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="276" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
         <v>11</v>
       </c>
@@ -10186,7 +10176,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="277" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
         <v>20</v>
       </c>
@@ -10221,7 +10211,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="278" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
         <v>24</v>
       </c>
@@ -10256,7 +10246,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="279" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
         <v>15</v>
       </c>
@@ -10291,7 +10281,7 @@
         <v>14.8</v>
       </c>
     </row>
-    <row r="280" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
         <v>17</v>
       </c>
@@ -10326,7 +10316,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="281" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
         <v>11</v>
       </c>
@@ -10361,7 +10351,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="282" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
         <v>15</v>
       </c>
@@ -10396,7 +10386,7 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="283" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
         <v>15</v>
       </c>
@@ -10431,7 +10421,7 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="284" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
         <v>15</v>
       </c>
@@ -10466,7 +10456,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="285" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
         <v>15</v>
       </c>
@@ -10501,7 +10491,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="286" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
         <v>15</v>
       </c>
@@ -10536,7 +10526,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="287" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
         <v>20</v>
       </c>
@@ -10571,7 +10561,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="288" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
         <v>11</v>
       </c>
@@ -10606,7 +10596,7 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="289" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
         <v>11</v>
       </c>
@@ -10676,7 +10666,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="291" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
         <v>11</v>
       </c>
@@ -10738,9 +10728,7 @@
       <c r="K293" s="2"/>
     </row>
     <row r="294" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A294" s="4" t="s">
-        <v>28</v>
-      </c>
+      <c r="A294" s="5"/>
       <c r="B294" s="2"/>
       <c r="C294" s="2"/>
       <c r="D294" s="2"/>
@@ -10753,9 +10741,7 @@
       <c r="K294" s="2"/>
     </row>
     <row r="295" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A295" s="5" t="s">
-        <v>29</v>
-      </c>
+      <c r="A295" s="5"/>
       <c r="B295" s="2"/>
       <c r="C295" s="2"/>
       <c r="D295" s="2"/>
@@ -10847,11 +10833,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:K291" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="Incineração"/>
-      </filters>
-    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A8:K290">
       <sortCondition descending="1" ref="F1:F291"/>
     </sortState>
